--- a/lessons/sorting/excels/remarks_required.xlsx
+++ b/lessons/sorting/excels/remarks_required.xlsx
@@ -162,12 +162,12 @@
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -let (10:59:27.295), -} (10:59:50.413), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00)</t>
+        <t>-i (10:38:53.739) ~0.00, -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -let (10:59:27.295), -} (10:59:50.413), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
       <text>
-        <t>(, ), ;, array, bubbleSort, let</t>
+        <t>let</t>
       </text>
     </comment>
     <comment ref="H5" authorId="0" shapeId="0">
@@ -177,17 +177,17 @@
     </comment>
     <comment ref="J5" authorId="0" shapeId="0">
       <text>
-        <t>+( (00:00:00), +) (00:00:00), +; (00:00:00), +array (00:00:00), +bubbleSort (00:00:00), +let (00:00:00), -var (10:59:12.196), -} (11:08:40.006)</t>
+        <t>+let (00:00:00), -var (10:59:12.196), -} (11:08:40.006)</t>
       </text>
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>-var (10:59:12.196), -} (11:08:40.006), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
+        <t>-var (10:59:12.196) ~0.00, -} (11:08:40.006), +let (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
       <text>
-        <t>( (x2), ) (x2), ;, array (x2), bubbleSort (x2), function, getElementByClassName, updatebars, {, }</t>
+        <t>(, ), array, bubbleSort, function, getElementByClassName, updatebars, {, }</t>
       </text>
     </comment>
     <comment ref="H9" authorId="0" shapeId="0">
@@ -197,12 +197,12 @@
     </comment>
     <comment ref="J9" authorId="0" shapeId="0">
       <text>
-        <t>+( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +array (00:00:00), +array (00:00:00), +bubbleSort (00:00:00), +bubbleSort (00:00:00), +function (00:00:00), +getElementByClassName (00:00:00), +updatebars (00:00:00), +{ (00:00:00), +} (00:00:00), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891)</t>
+        <t>+( (00:00:00), +) (00:00:00), +array (00:00:00), +bubbleSort (00:00:00), +function (00:00:00), +getElementByClassName (00:00:00), +updatebars (00:00:00), +{ (00:00:00), +} (00:00:00), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891)</t>
       </text>
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>-updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+        <t>-updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
@@ -235,16 +235,6 @@
         <t>+&amp; (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +* (00:00:00), +, (00:00:00), +, (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +50 (00:00:00), +50 (00:00:00), +FYI (00:00:00), +a (00:00:00), +adding (00:00:00), +aligns (00:00:00), +an (00:00:00), +and (00:00:00), +are (00:00:00), +array (00:00:00), +be (00:00:00), +bettween (00:00:00), +center (00:00:00), +code (00:00:00), +combined (00:00:00), +const (00:00:00), +contatenation (00:00:00), +content (00:00:00), +days (00:00:00), +divs (00:00:00), +do (00:00:00), +due (00:00:00), +generates (00:00:00), +generates (00:00:00), +handle (00:00:00), +in (00:00:00), +insta (00:00:00), +is (00:00:00), +items (00:00:00), +let (00:00:00), +loop (00:00:00), +loop (00:00:00), +mainly (00:00:00), +make (00:00:00), +modern (00:00:00), +new (00:00:00), +norm (00:00:00), +not (00:00:00), +not (00:00:00), +now (00:00:00), +now (00:00:00), +old (00:00:00), +on (00:00:00), +plus (00:00:00), +rare (00:00:00), +refresh (00:00:00), +sets (00:00:00), +speed (00:00:00), +stuff (00:00:00), +swapping (00:00:00), +the (00:00:00), +the (00:00:00), +them (00:00:00), +these (00:00:00), +these (00:00:00), +this (00:00:00), +three (00:00:00), +to (00:00:00), +to (00:00:00), +to (00:00:00), +used (00:00:00), +uses (00:00:00), +var (00:00:00), +very (00:00:00), +we (00:00:00), +while (00:00:00), +while (00:00:00), +will (00:00:00), +with (00:00:00), -between (10:31:51.888), -+ (10:50:51.369), -concatenation (10:50:59.133), -because (10:51:02.635), -% (10:51:07.534)</t>
       </text>
     </comment>
-    <comment ref="J24" authorId="0" shapeId="0">
-      <text>
-        <t>-; (10:42:36.565)</t>
-      </text>
-    </comment>
-    <comment ref="Q24" authorId="0" shapeId="0">
-      <text>
-        <t>-; (10:42:36.565)</t>
-      </text>
-    </comment>
     <comment ref="E25" authorId="0" shapeId="0">
       <text>
         <t>ClassList, getElementByClassName, lenght (x3), promise</t>
@@ -262,7 +252,7 @@
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H30" authorId="0" shapeId="0">
@@ -277,7 +267,7 @@
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
       <text>
-        <t>, (x3), aee, bubblesort, promise, (*, )*, ;*, array*</t>
+        <t>, (x3), aee, bubblesort, promise</t>
       </text>
     </comment>
     <comment ref="H36" authorId="0" shapeId="0">
@@ -287,22 +277,22 @@
     </comment>
     <comment ref="J36" authorId="0" shapeId="0">
       <text>
-        <t>+, (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -Promise (11:13:54.982)</t>
+        <t>+, (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -bubbleSort (11:08:34.118), -Promise (11:13:54.982)</t>
       </text>
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -Promise (11:13:54.982), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+        <t>-. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -bubbleSort (11:08:34.118) ~0.90, -Promise (11:13:54.982) ~0.86, +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
       <text>
-        <t>(, ), /, ;, array (x2), bubbleSort</t>
+        <t>/, array</t>
       </text>
     </comment>
     <comment ref="J42" authorId="0" shapeId="0">
       <text>
-        <t>+( (00:00:00), +) (00:00:00), +/ (00:00:00), +; (00:00:00), +array (00:00:00), +array (00:00:00), +bubbleSort (00:00:00), -let (10:38:51.733), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100)</t>
+        <t>+/ (00:00:00), +array (00:00:00), -let (10:38:51.733), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100)</t>
       </text>
     </comment>
     <comment ref="M42" authorId="0" shapeId="0">
@@ -312,7 +302,7 @@
     </comment>
     <comment ref="Q42" authorId="0" shapeId="0">
       <text>
-        <t>-let (10:38:51.733), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +array (00:00:00)</t>
+        <t>-let (10:38:51.733), -let (11:09:56.455), -bars (11:09:58.993) ~0.20, -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D45" authorId="0" shapeId="0">
@@ -352,7 +342,7 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), +tittle (00:00:00), +visualizer (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, +tittle (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
@@ -362,7 +352,7 @@
     </comment>
     <comment ref="Q48" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -document (10:37:47.323), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -382,7 +372,7 @@
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), +getElementsByClassname (00:00:00)</t>
+        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, +getElementsByClassname (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H51" authorId="0" shapeId="0">
@@ -427,12 +417,12 @@
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="H62" authorId="0" shapeId="0">
@@ -472,12 +462,12 @@
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -document (11:09:24.920), -getElementsByClassName (11:09:28.891), -bars (11:09:58.993), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +- (00:00:00), +1 (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -document (11:09:24.920) ~0.10, -getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +- (00:00:00), +1 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
       <text>
-        <t>(, ), ;, &gt;, array, bats, bubbleSort, bubblesort, promise</t>
+        <t>&gt;, bats, bubblesort, promise</t>
       </text>
     </comment>
     <comment ref="H70" authorId="0" shapeId="0">
@@ -487,7 +477,7 @@
     </comment>
     <comment ref="J70" authorId="0" shapeId="0">
       <text>
-        <t>+( (00:00:00), +) (00:00:00), +; (00:00:00), +&gt; (00:00:00), +array (00:00:00), +bats (00:00:00), +bubbleSort (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), -&lt; (10:27:15.917), -bubbleSort (10:57:42.836), -i (10:59:29.253), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982)</t>
+        <t>+&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), -&lt; (10:27:15.917), -bubbleSort (10:57:42.836), -i (10:59:29.253), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982)</t>
       </text>
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
@@ -497,7 +487,7 @@
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D72" authorId="0" shapeId="0">
@@ -517,7 +507,7 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), +tittle (00:00:00), +visualizer (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, +tittle (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
@@ -527,7 +517,7 @@
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -document (10:37:47.323), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E75" authorId="0" shapeId="0">
@@ -542,7 +532,7 @@
     </comment>
     <comment ref="Q75" authorId="0" shapeId="0">
       <text>
-        <t>-createElement (10:39:45.021), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342), -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -setTimeout (11:14:18.857), +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+        <t>-createElement (10:39:45.021) ~0.93, -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -585,24 +575,9 @@
         <t>+, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +0 (00:00:00), +0 (00:00:00), +2 (00:00:00), +2nd (00:00:00), +75 (00:00:00), +as (00:00:00), +etc (00:00:00), +such (00:00:00), -and (10:31:53.378), -here (10:50:52.605), -second (10:51:05.518), -" (10:51:07.103), -% (10:51:07.534), -" (10:51:07.847)</t>
       </text>
     </comment>
-    <comment ref="E83" authorId="0" shapeId="0">
-      <text>
-        <t>(, ), ;, array, bubbleSort</t>
-      </text>
-    </comment>
     <comment ref="H83" authorId="0" shapeId="0">
       <text>
         <t>+concatentaion (00:00:00), +generates (00:00:00), +it (00:00:00), +num (00:00:00), -numbers (10:31:49.525), -concatenation (10:50:59.133)</t>
-      </text>
-    </comment>
-    <comment ref="J83" authorId="0" shapeId="0">
-      <text>
-        <t>+( (00:00:00), +) (00:00:00), +; (00:00:00), +array (00:00:00), +bubbleSort (00:00:00)</t>
-      </text>
-    </comment>
-    <comment ref="Q83" authorId="0" shapeId="0">
-      <text>
-        <t>+bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1173,7 +1148,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -let (10:59:27.295), -} (10:59:50.413), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00)</t>
+          <t>-i (10:38:53.739) ~0.00, -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -let (10:59:27.295), -} (10:59:50.413), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1203,11 +1178,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(, ), ;, array, bubbleSort, let</t>
+          <t>let</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1222,11 +1197,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>98.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+( (00:00:00), +) (00:00:00), +; (00:00:00), +array (00:00:00), +bubbleSort (00:00:00), +let (00:00:00), -var (10:59:12.196), -} (11:08:40.006)</t>
+          <t>+let (00:00:00), -var (10:59:12.196), -} (11:08:40.006)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1239,11 +1214,11 @@
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>97.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-var (10:59:12.196), -} (11:08:40.006), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
+          <t>-var (10:59:12.196) ~0.00, -} (11:08:40.006), +let (00:00:00)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1381,11 +1356,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>( (x2), ) (x2), ;, array (x2), bubbleSort (x2), function, getElementByClassName, updatebars, {, }</t>
+          <t>(, ), array, bubbleSort, function, getElementByClassName, updatebars, {, }</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1400,11 +1375,11 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +array (00:00:00), +array (00:00:00), +bubbleSort (00:00:00), +bubbleSort (00:00:00), +function (00:00:00), +getElementByClassName (00:00:00), +updatebars (00:00:00), +{ (00:00:00), +} (00:00:00), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891)</t>
+          <t>+( (00:00:00), +) (00:00:00), +array (00:00:00), +bubbleSort (00:00:00), +function (00:00:00), +getElementByClassName (00:00:00), +updatebars (00:00:00), +{ (00:00:00), +} (00:00:00), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1421,11 +1396,11 @@
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+          <t>-updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2068,13 +2043,9 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>-; (10:42:36.565)</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>100</v>
@@ -2085,13 +2056,9 @@
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>-; (10:42:36.565)</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>_</t>
@@ -2159,7 +2126,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2611,7 +2578,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>, (x3), aee, bubblesort, promise, (*, )*, ;*, array*</t>
+          <t>, (x3), aee, bubblesort, promise</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2626,11 +2593,11 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>96.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>+, (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -Promise (11:13:54.982)</t>
+          <t>+, (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -bubbleSort (11:08:34.118), -Promise (11:13:54.982)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2643,11 +2610,11 @@
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>94.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -Promise (11:13:54.982), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+          <t>-. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -bubbleSort (11:08:34.118) ~0.90, -Promise (11:13:54.982) ~0.86, +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -2861,11 +2828,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>(, ), /, ;, array (x2), bubbleSort</t>
+          <t>/, array</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2876,11 +2843,11 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>88.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>+( (00:00:00), +) (00:00:00), +/ (00:00:00), +; (00:00:00), +array (00:00:00), +array (00:00:00), +bubbleSort (00:00:00), -let (10:38:51.733), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100)</t>
+          <t>+/ (00:00:00), +array (00:00:00), -let (10:38:51.733), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2897,11 +2864,11 @@
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
-        <v>83.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>-let (10:38:51.733), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +array (00:00:00)</t>
+          <t>-let (10:38:51.733), -let (11:09:56.455), -bars (11:09:58.993) ~0.20, -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -3191,7 +3158,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), +tittle (00:00:00), +visualizer (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, +tittle (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3207,7 +3174,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -document (10:37:47.323), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3315,7 +3282,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), +getElementsByClassname (00:00:00)</t>
+          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, +getElementsByClassname (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -3741,7 +3708,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4165,7 +4132,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -document (11:09:24.920), -getElementsByClassName (11:09:28.891), -bars (11:09:58.993), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +- (00:00:00), +1 (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -document (11:09:24.920) ~0.10, -getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +- (00:00:00), +1 (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4233,11 +4200,11 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>(, ), ;, &gt;, array, bats, bubbleSort, bubblesort, promise</t>
+          <t>&gt;, bats, bubblesort, promise</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4252,11 +4219,11 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>97.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>+( (00:00:00), +) (00:00:00), +; (00:00:00), +&gt; (00:00:00), +array (00:00:00), +bats (00:00:00), +bubbleSort (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), -&lt; (10:27:15.917), -bubbleSort (10:57:42.836), -i (10:59:29.253), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982)</t>
+          <t>+&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), -&lt; (10:27:15.917), -bubbleSort (10:57:42.836), -i (10:59:29.253), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4273,11 +4240,11 @@
       </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
-        <v>96.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -4389,7 +4356,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), +tittle (00:00:00), +visualizer (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, +tittle (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4405,7 +4372,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -document (10:37:47.323), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -4563,7 +4530,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>-createElement (10:39:45.021), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342), -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -setTimeout (11:14:18.857), +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+          <t>-createElement (10:39:45.021) ~0.93, -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -4963,13 +4930,9 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>(, ), ;, array, bubbleSort</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>99.3</v>
       </c>
@@ -4982,13 +4945,9 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>+( (00:00:00), +) (00:00:00), +; (00:00:00), +array (00:00:00), +bubbleSort (00:00:00)</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>100</v>
@@ -4999,13 +4958,9 @@
       </c>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>+bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00)</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>_</t>
